--- a/data/trans_orig/P1434-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1434-Habitat-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,19 +526,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos de próstata en 2007</t>
+          <t>Población con diagnóstico de trastornos de próstata en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -733,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27064</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +688,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27490</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>17523</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>10729</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>27064</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>666948</t>
+          <t>666522</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>683283</t>
+          <t>683337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +766,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>676489</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>666522</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683337</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>676489</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>666948</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>683283</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>96,1%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -984,70 +854,35 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>683</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>694012</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>694012</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>694012</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>694012</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>694012</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>694012</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1076,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>24507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46798</t>
+          <t>47222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,82 +926,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34283</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>34283</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>23689</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>46798</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>915002</t>
+          <t>914578</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>938111</t>
+          <t>937293</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1004,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>862</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>927517</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>914578</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>937293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>927517</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>915002</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>938111</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>95,13%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -1327,70 +1092,35 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>896</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>961800</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>961800</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>961800</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>961800</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>961800</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>961800</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1419,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33795</t>
+          <t>33142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,82 +1164,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22815</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>22815</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>14274</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>33795</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>644714</t>
+          <t>645367</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664235</t>
+          <t>663680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,82 +1242,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>655694</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>645367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>663680</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>655694</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>644714</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>664235</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -1670,70 +1330,35 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>678509</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>678509</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>678509</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>678509</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>678509</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>678509</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1762,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23101</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44269</t>
+          <t>42382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,82 +1402,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31568</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42382</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>31568</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>23101</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>44269</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>897953</t>
+          <t>899840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>919121</t>
+          <t>919842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,82 +1480,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>958</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>910654</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>899840</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>919842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>910654</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>897953</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>919121</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,65%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -2013,70 +1568,35 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>994</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>942222</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>942222</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>942222</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>994</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>942222</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>942222</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>942222</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2105,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86256</t>
+          <t>86266</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125642</t>
+          <t>127218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,77 +1645,42 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106188</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>127218</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>106188</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>86256</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>125642</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3150901</t>
+          <t>3149325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3190287</t>
+          <t>3190277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +1718,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2243,70 +1728,35 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3170355</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3149325</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3190277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3170355</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3150901</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3190287</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>96,17%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>97,37%</t>
         </is>
@@ -2356,70 +1806,35 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3276543</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3276543</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3276543</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3214</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3276543</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3276543</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3276543</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2433,14 +1848,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2454,7 +1868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2473,19 +1887,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos de próstata en 2012</t>
+          <t>Población con diagnóstico de trastornos de próstata en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2502,7 +1909,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2511,17 +1918,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2592,41 +1988,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2649,13 +2010,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2680,12 +2034,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14031</t>
+          <t>13757</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33960</t>
+          <t>33691</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,82 +2049,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22435</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13757</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>22435</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>14031</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>33960</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2112,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>669509</t>
+          <t>669778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>689438</t>
+          <t>689712</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,82 +2127,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>654</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>681034</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>669778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>689712</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>681034</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>669509</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>689438</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>95,17%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -2931,70 +2215,35 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>674</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>703469</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>703469</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>703469</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>703469</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>703469</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>703469</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3023,12 +2272,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23579</t>
+          <t>22282</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46838</t>
+          <t>45679</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,82 +2287,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32936</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22282</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45679</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>32936</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>23579</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>46838</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +2350,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>968918</t>
+          <t>970077</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>992177</t>
+          <t>993474</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,82 +2365,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>904</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>982820</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>970077</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>993474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>904</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>982820</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>968918</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>992177</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,76%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -3274,70 +2453,35 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>935</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1015756</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1015756</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1015756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1015756</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1015756</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1015756</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3366,12 +2510,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17774</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41062</t>
+          <t>42186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,82 +2525,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27213</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>27213</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>17774</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>41062</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +2588,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>716561</t>
+          <t>715437</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>739849</t>
+          <t>740041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,82 +2603,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>666</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>730410</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>715437</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>740041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>730410</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>716561</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>739849</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,41%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>94,58%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,65%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3617,70 +2691,35 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>689</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>757623</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>757623</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>757623</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>757623</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>757623</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>757623</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3709,12 +2748,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29310</t>
+          <t>30311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56083</t>
+          <t>56868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,82 +2763,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41825</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30311</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>41825</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>29310</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>56083</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +2826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>891656</t>
+          <t>890871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>918429</t>
+          <t>917428</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,82 +2841,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>872</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>905914</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>890871</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>917428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>905914</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>891656</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>918429</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>95,59%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -3960,70 +2929,35 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>910</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>947739</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>947739</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>947739</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>947739</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>947739</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>947739</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4052,12 +2986,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101366</t>
+          <t>102054</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>146990</t>
+          <t>149623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,82 +3001,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124409</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149623</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>124409</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>101366</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>146990</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +3064,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3277597</t>
+          <t>3274964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3323221</t>
+          <t>3322533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,82 +3079,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3300178</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3274964</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3322533</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3096</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3300178</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3277597</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3323221</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>95,71%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -4303,70 +3167,35 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3424587</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3424587</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3424587</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3208</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3424587</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3424587</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3424587</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4380,14 +3209,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -4401,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4420,19 +3248,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos de próstata en 2016</t>
+          <t>Población con diagnóstico de trastornos de próstata en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4449,7 +3270,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4458,17 +3279,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -4539,41 +3349,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -4596,13 +3371,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4627,12 +3395,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36095</t>
+          <t>35488</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,77 +3415,42 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25341</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35488</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>25341</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>16962</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>36095</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +3473,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>638705</t>
+          <t>639312</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>657838</t>
+          <t>657858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,7 +3488,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4765,70 +3498,35 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>625</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>649459</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>639312</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>657858</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>649459</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>638705</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>657838</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>94,65%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>97,49%</t>
         </is>
@@ -4878,70 +3576,35 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>652</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674800</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>674800</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>674800</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>674800</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>674800</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4970,12 +3633,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16005</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35143</t>
+          <t>36750</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,82 +3648,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24826</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>24826</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>16005</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>35143</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +3711,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>987288</t>
+          <t>985681</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1006426</t>
+          <t>1005755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,82 +3726,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>924</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>997605</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>985681</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1005755</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>997605</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>987288</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1006426</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -5221,70 +3814,35 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>951</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1022431</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1022431</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1022431</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1022431</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1022431</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1022431</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5313,12 +3871,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34310</t>
+          <t>35497</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,82 +3886,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23438</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15680</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>23438</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>15297</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>34310</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +3949,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>725242</t>
+          <t>724055</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>744255</t>
+          <t>743872</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,82 +3964,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>736114</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>724055</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>743872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>736114</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>725242</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>744255</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>95,48%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -5564,70 +4052,35 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>696</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>759552</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>759552</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>759552</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>759552</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>759552</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>759552</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5656,12 +4109,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26781</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49111</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,82 +4124,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35397</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>35397</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>26781</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>49111</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +4187,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>888456</t>
+          <t>889962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>910786</t>
+          <t>912747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,82 +4202,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>895</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>902170</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>889962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>912747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>902170</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>888456</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>910786</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>96,22%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>94,76%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -5907,70 +4290,35 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>932</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>937567</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>937567</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>937567</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>937567</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>937567</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>937567</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5999,12 +4347,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89248</t>
+          <t>92176</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>130833</t>
+          <t>133426</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,82 +4362,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>109002</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92176</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>109002</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>89248</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>130833</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +4425,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3263517</t>
+          <t>3260924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3305102</t>
+          <t>3302174</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,82 +4440,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3285348</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3260924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3302174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3117</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3285348</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3263517</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3305102</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>96,15%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>97,37%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -6250,70 +4528,35 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3394350</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3394350</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3394350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3394350</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3394350</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3394350</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6327,14 +4570,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -6348,7 +4590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6367,19 +4609,12 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de trastornos de próstata en 2023</t>
+          <t>Población con diagnóstico de trastornos de próstata en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6396,7 +4631,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6405,17 +4640,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -6486,41 +4710,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -6543,13 +4732,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -6574,12 +4756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35850</t>
+          <t>34931</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56948</t>
+          <t>57106</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,82 +4771,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44743</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34931</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57106</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>44743</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>35850</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>56948</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +4834,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>577160</t>
+          <t>577002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>598258</t>
+          <t>599177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,82 +4849,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>653</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>589365</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>577002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>599177</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>589365</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>577160</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>598258</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>92,94%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>91,02%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>94,35%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -6825,70 +4937,35 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>728</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>634108</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>634108</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>634108</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>728</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>634108</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>634108</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>634108</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6917,12 +4994,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24218</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66123</t>
+          <t>64503</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,82 +5009,47 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47414</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64503</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>47414</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>24218</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>66123</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +5072,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1122299</t>
+          <t>1123919</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1164204</t>
+          <t>1163054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,82 +5087,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>887</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1141008</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1123919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1163054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1141008</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1122299</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1164204</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>96,01%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -7168,70 +5175,35 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>960</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1188422</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1188422</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1188422</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1188422</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1188422</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1188422</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7260,12 +5232,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38053</t>
+          <t>38658</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,82 +5247,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27205</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38658</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>27205</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>19249</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>38053</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +5310,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660249</t>
+          <t>659644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679053</t>
+          <t>678851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,82 +5325,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>633</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>671097</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>659644</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>678851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>671097</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>660249</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>679053</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,1%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -7511,70 +5413,35 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>669</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>698302</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>698302</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>698302</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>698302</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>698302</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>698302</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7603,12 +5470,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50093</t>
+          <t>49381</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75197</t>
+          <t>75694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,82 +5485,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60876</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49381</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>60876</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>50093</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>75197</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +5548,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>843982</t>
+          <t>843485</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>869086</t>
+          <t>869798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,82 +5563,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>908</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>858303</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>843485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>869798</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>908</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>858303</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>843982</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>869086</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>91,82%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -7854,70 +5651,35 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>919179</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>919179</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>919179</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>919179</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>919179</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>919179</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7946,12 +5708,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141270</t>
+          <t>139447</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>207856</t>
+          <t>204671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,82 +5723,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>278</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>180237</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139447</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>180237</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>141270</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>207856</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>6,04%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +5786,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3232155</t>
+          <t>3235340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3298741</t>
+          <t>3300564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,82 +5801,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3259774</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3235340</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3300564</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>3259774</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3232155</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3298741</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>94,76%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>93,96%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>95,89%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -8197,70 +5889,35 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3440011</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3440011</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3440011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3359</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>3440011</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>3440011</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>3440011</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8274,14 +5931,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P1434-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1434-Habitat-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27490</t>
+          <t>26858</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27490</t>
+          <t>26858</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>666522</t>
+          <t>667154</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>683337</t>
+          <t>683301</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>666522</t>
+          <t>667154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>683337</t>
+          <t>683301</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24507</t>
+          <t>23737</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47222</t>
+          <t>47362</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24507</t>
+          <t>23737</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47222</t>
+          <t>47362</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>914578</t>
+          <t>914438</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>937293</t>
+          <t>938063</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>914578</t>
+          <t>914438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>937293</t>
+          <t>938063</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33142</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33142</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>645367</t>
+          <t>643004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663680</t>
+          <t>663119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645367</t>
+          <t>643004</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>663680</t>
+          <t>663119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>22520</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42382</t>
+          <t>43489</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22380</t>
+          <t>22520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42382</t>
+          <t>43489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>899840</t>
+          <t>898733</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>919842</t>
+          <t>919702</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>899840</t>
+          <t>898733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>919842</t>
+          <t>919702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86266</t>
+          <t>88774</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127218</t>
+          <t>126899</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>86266</t>
+          <t>88774</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>127218</t>
+          <t>126899</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3149325</t>
+          <t>3149644</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3190277</t>
+          <t>3187769</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3149325</t>
+          <t>3149644</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3190277</t>
+          <t>3187769</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -2034,12 +2034,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33691</t>
+          <t>35827</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33691</t>
+          <t>35827</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>669778</t>
+          <t>667642</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>689712</t>
+          <t>688869</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>669778</t>
+          <t>667642</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>689712</t>
+          <t>688869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22282</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>45620</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22282</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>45620</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>970077</t>
+          <t>970136</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>993474</t>
+          <t>992598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>970077</t>
+          <t>970136</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>993474</t>
+          <t>992598</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>17770</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42186</t>
+          <t>41416</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>17770</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42186</t>
+          <t>41416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>715437</t>
+          <t>716207</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>740041</t>
+          <t>739853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>715437</t>
+          <t>716207</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>740041</t>
+          <t>739853</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30311</t>
+          <t>30264</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56868</t>
+          <t>57231</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30311</t>
+          <t>30264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56868</t>
+          <t>57231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>890871</t>
+          <t>890508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>917428</t>
+          <t>917475</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>890871</t>
+          <t>890508</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>917428</t>
+          <t>917475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -2986,12 +2986,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102054</t>
+          <t>101960</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149623</t>
+          <t>147982</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102054</t>
+          <t>101960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149623</t>
+          <t>147982</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3274964</t>
+          <t>3276605</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3322533</t>
+          <t>3322627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3274964</t>
+          <t>3276605</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3322533</t>
+          <t>3322627</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35488</t>
+          <t>35175</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35488</t>
+          <t>35175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -3473,12 +3473,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>639312</t>
+          <t>639625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>657858</t>
+          <t>658811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>639312</t>
+          <t>639625</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>657858</t>
+          <t>658811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3523,12 +3523,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36750</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36750</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>985681</t>
+          <t>985601</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1005755</t>
+          <t>1005628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>985681</t>
+          <t>985601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1005755</t>
+          <t>1005628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,36%</t>
         </is>
       </c>
     </row>
@@ -3871,12 +3871,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15680</t>
+          <t>15442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35497</t>
+          <t>34644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15680</t>
+          <t>15442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35497</t>
+          <t>34644</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3949,12 +3949,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>724055</t>
+          <t>724908</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>743872</t>
+          <t>744110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>724055</t>
+          <t>724908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>743872</t>
+          <t>744110</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24820</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47605</t>
+          <t>47689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24820</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47605</t>
+          <t>47689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4187,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>889962</t>
+          <t>889878</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>912747</t>
+          <t>912906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>889962</t>
+          <t>889878</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>912747</t>
+          <t>912906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -4347,12 +4347,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92176</t>
+          <t>91109</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133426</t>
+          <t>131154</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4362,12 +4362,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92176</t>
+          <t>91109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133426</t>
+          <t>131154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4425,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3260924</t>
+          <t>3263196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3302174</t>
+          <t>3303241</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3260924</t>
+          <t>3263196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3302174</t>
+          <t>3303241</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -4751,32 +4751,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44743</t>
+          <t>48045</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34931</t>
+          <t>38090</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57106</t>
+          <t>59865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4786,32 +4786,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44743</t>
+          <t>48045</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34931</t>
+          <t>38090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57106</t>
+          <t>59865</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -4829,32 +4829,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>589365</t>
+          <t>641288</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>577002</t>
+          <t>629468</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>599177</t>
+          <t>651243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4864,32 +4864,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>589365</t>
+          <t>641288</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>577002</t>
+          <t>629468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>599177</t>
+          <t>651243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -4907,17 +4907,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634108</t>
+          <t>689333</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634108</t>
+          <t>689333</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634108</t>
+          <t>689333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4942,17 +4942,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>634108</t>
+          <t>689333</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>634108</t>
+          <t>689333</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>634108</t>
+          <t>689333</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4989,32 +4989,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47414</t>
+          <t>50985</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>39883</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64503</t>
+          <t>64225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5024,32 +5024,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47414</t>
+          <t>50985</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>39883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64503</t>
+          <t>64225</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -5067,32 +5067,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1141008</t>
+          <t>993277</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1123919</t>
+          <t>980037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1163054</t>
+          <t>1004379</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5102,32 +5102,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1141008</t>
+          <t>993277</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1123919</t>
+          <t>980037</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1163054</t>
+          <t>1004379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -5145,17 +5145,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1188422</t>
+          <t>1044262</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1188422</t>
+          <t>1044262</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1188422</t>
+          <t>1044262</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5180,17 +5180,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1188422</t>
+          <t>1044262</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1188422</t>
+          <t>1044262</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1188422</t>
+          <t>1044262</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5227,32 +5227,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>30375</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19451</t>
+          <t>21637</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>42732</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5262,32 +5262,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>30375</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19451</t>
+          <t>21637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>42732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -5305,32 +5305,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>671097</t>
+          <t>765733</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>659644</t>
+          <t>753376</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678851</t>
+          <t>774471</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5340,32 +5340,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>671097</t>
+          <t>765733</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>659644</t>
+          <t>753376</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>678851</t>
+          <t>774471</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -5383,17 +5383,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>698302</t>
+          <t>796108</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>698302</t>
+          <t>796108</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>698302</t>
+          <t>796108</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5418,17 +5418,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>698302</t>
+          <t>796108</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>698302</t>
+          <t>796108</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>698302</t>
+          <t>796108</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5465,32 +5465,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60876</t>
+          <t>63670</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49381</t>
+          <t>51781</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75694</t>
+          <t>76775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5500,32 +5500,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60876</t>
+          <t>63670</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49381</t>
+          <t>51781</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75694</t>
+          <t>76775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -5543,32 +5543,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>858303</t>
+          <t>918886</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>843485</t>
+          <t>905781</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>869798</t>
+          <t>930775</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5578,32 +5578,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>858303</t>
+          <t>918886</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>843485</t>
+          <t>905781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>869798</t>
+          <t>930775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -5621,17 +5621,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>919179</t>
+          <t>982556</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>919179</t>
+          <t>982556</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>919179</t>
+          <t>982556</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>919179</t>
+          <t>982556</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>919179</t>
+          <t>982556</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>919179</t>
+          <t>982556</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5703,32 +5703,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>180237</t>
+          <t>193076</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139447</t>
+          <t>170780</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204671</t>
+          <t>217408</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5738,32 +5738,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>180237</t>
+          <t>193076</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139447</t>
+          <t>170780</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204671</t>
+          <t>217408</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -5781,32 +5781,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3259774</t>
+          <t>3319184</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3235340</t>
+          <t>3294852</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3300564</t>
+          <t>3341480</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5816,32 +5816,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3259774</t>
+          <t>3319184</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3235340</t>
+          <t>3294852</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3300564</t>
+          <t>3341480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -5859,17 +5859,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5894,17 +5894,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3440011</t>
+          <t>3512260</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
